--- a/giro_da_praça_ofertas - Copia.xlsx
+++ b/giro_da_praça_ofertas - Copia.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1927,49 +1963,49 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>SABONETE ANTIBACTERIAL REXONA 84G ERVA DOCE</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
+          <t>SABONETE REXONA 84G</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>ANTIBACTERIANO, BAMBOO FRESH, ERVA DOCE, ORCHID FRESH</t>
+        </is>
+      </c>
       <c r="F61" s="6" t="n">
         <v>2.49</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/TERÇA - OFERTAS 03 E 04/11/25</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>#04 HIGIENE PESSOAL - SABONETE</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>144144</v>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>SABONETE REXONA 84G</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>ANTIBACTERIANO, BAMBOO FRESH, ORCHID FRESH</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>2.49</v>
-      </c>
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - OFERTAS 03 E 04/11/25</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="n">
+        <v>10.49</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1983,16 +2019,16 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>104406</v>
+        <v>104410</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="6" t="n">
-        <v>10.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="65">
@@ -2007,16 +2043,16 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>104410</v>
+        <v>104405</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
+          <t>REFRIGERANTE SUKITA 2L LARANJA</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="6" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="66">
@@ -2027,58 +2063,58 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>104405</v>
+        <v>286325</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE SUKITA 2L LARANJA</t>
+          <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="6" t="n">
-        <v>6.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/TERÇA - OFERTAS 03 E 04/11/25</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>286325</v>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>SUCO AURORA TP 1,5L UVA TINTO</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="n">
-        <v>21.99</v>
-      </c>
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AVES 03/11/25</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>105842</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>ASA DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="6" t="n">
+        <v>13.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
+          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2087,22 +2123,22 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>105842</v>
+        <v>326587</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t>CORAÇÃO DE FRANGO SEARA PCT 1KG</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="6" t="n">
-        <v>13.99</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
+          <t>SEGUNDA - AVES 03/11/25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2111,22 +2147,22 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>326587</v>
+        <v>105838</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>CORAÇÃO DE FRANGO SEARA PCT 1KG</t>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="6" t="n">
-        <v>27</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
+          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2135,22 +2171,22 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>105838</v>
+        <v>111565</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t>COXA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="n">
-        <v>10.99</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
+          <t>SEGUNDA - AVES 03/11/25</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2159,22 +2195,22 @@
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>111565</v>
+        <v>105840</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA BDJ 1KG</t>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="6" t="n">
-        <v>14.39</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
+          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2183,40 +2219,40 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>105840</v>
+        <v>114271</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t>FILEZINHO DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="6" t="n">
-        <v>13.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AVES 03/11/25</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
-        <v>114271</v>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>FILEZINHO DE FRANGO SADIA BDJ 1KG</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="6" t="n">
-        <v>24.99</v>
+      <c r="C74" s="8" t="n">
+        <v>109597</v>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>FILÉ DE PEITO DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr"/>
+      <c r="F74" s="10" t="n">
+        <v>20.99</v>
       </c>
     </row>
     <row r="75">
@@ -2231,16 +2267,16 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>109597</v>
+        <v>119927</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>FILÉ DE PEITO DE FRANGO KG</t>
+          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="6" t="n">
-        <v>18.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="76">
@@ -2255,22 +2291,22 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>119927</v>
+        <v>185934</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+          <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="6" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
+          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -2279,16 +2315,16 @@
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>185934</v>
+        <v>108783</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
+          <t>MEIO DA ASA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="6" t="n">
-        <v>10.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="78">
@@ -2303,211 +2339,451 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>108783</v>
+        <v>108771</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>MEIO DA ASA DE FRANGO SADIA BDJ 1KG</t>
+          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="6" t="n">
-        <v>29.99</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>239334</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr"/>
+      <c r="F79" s="10" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>105456</v>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="10" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>105468</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr"/>
+      <c r="F81" s="10" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="10" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr"/>
+      <c r="F83" s="10" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>COXÃO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="10" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>132915</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>CUPIM FATIADO TEMPERADO KG</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr"/>
+      <c r="F85" s="10" t="n">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr"/>
+      <c r="F86" s="10" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="n">
+        <v>298422</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>SUINO CAIPIRA KG</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="10" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr"/>
+      <c r="F88" s="10" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 03/11/25</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="10" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AVES 03/11/25</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>228422</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="6" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AVES 03/11/25</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>105765</v>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="6" t="n">
+        <v>9.390000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AVES 03/11/25</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>105770</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="6" t="n">
+        <v>11.39</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>108771</v>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr"/>
-      <c r="F79" s="6" t="n">
-        <v>16.49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>252392</v>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="6" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>SEGUNDA - AVES 03/11/25</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
-        <v>228422</v>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="6" t="n">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>105765</v>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="6" t="n">
-        <v>9.390000000000001</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>105770</v>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="6" t="n">
-        <v>11.39</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="C94" s="3" t="n">
+        <v>286228</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>SALSICHA BOUA KG</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="6" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>252392</v>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="6" t="n">
-        <v>16.99</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA - AVES 03/11/25</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>286228</v>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>SALSICHA BOUA KG</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="6" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>170266</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO PERDIGÃO 100G FRANGO</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="6" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
-        <v>170266</v>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>STEAK EMPANADO PERDIGÃO 100G FRANGO</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr"/>
-      <c r="F85" s="6" t="n">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA - PERECIVEIS 03 E 04/11/25</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
+      <c r="C96" s="3" t="n">
         <v>138538</v>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>FRANGO, QUEIJO COM OREGANO</t>
         </is>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F96" s="6" t="n">
         <v>8.49</v>
       </c>
     </row>
